--- a/Inputs/Recycling_sources.xlsx
+++ b/Inputs/Recycling_sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Pablo\Programming\R\R Stanford\material-intensity\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4384CA-C278-4538-8353-0C583E56A8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D78CE96-CBEE-4283-99A7-4B72D5F16427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="46" r:id="rId9"/>
-    <pivotCache cacheId="45" r:id="rId10"/>
+    <pivotCache cacheId="10" r:id="rId9"/>
+    <pivotCache cacheId="16" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="763">
   <si>
     <t>Item</t>
   </si>
@@ -2371,9 +2371,6 @@
   </si>
   <si>
     <t>Average of Maximum share allowed / recommended</t>
-  </si>
-  <si>
-    <t>(Multiple Items)</t>
   </si>
 </sst>
 </file>
@@ -2585,28 +2582,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
@@ -2874,86 +2850,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Pablo Busch" refreshedDate="46301.38437511574" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="29" xr:uid="{5C9B316A-7DF0-48F3-8AC8-536953F8B8F0}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:K30" sheet="Max_secondary_content"/>
-  </cacheSource>
-  <cacheFields count="11">
-    <cacheField name="Region / standard" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Your region" numFmtId="0">
-      <sharedItems count="9">
-        <s v="Oceania"/>
-        <s v="East Asia"/>
-        <s v="Europe &amp; Russia"/>
-        <s v="Global"/>
-        <s v="North America"/>
-        <s v="Latin America"/>
-        <s v="South Asia"/>
-        <s v="—"/>
-        <s v="All"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="End-use" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Recycled material" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Variable" numFmtId="0">
-      <sharedItems containsBlank="1" count="3">
-        <s v="Max building"/>
-        <s v="Max Roads"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Valid" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="2">
-        <n v="1"/>
-        <n v="0"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Maximum share allowed / recommended" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="1" count="13">
-        <n v="0.3"/>
-        <n v="1"/>
-        <n v="0.2"/>
-        <s v="Coarse only (fines not allowed); RMA coarse &lt;100%"/>
-        <n v="0.7"/>
-        <n v="0.8"/>
-        <n v="0.6"/>
-        <n v="0.25"/>
-        <n v="0.1"/>
-        <n v="0"/>
-        <s v="100% RCA/RCB blends tested as unbound base/sub-base in cited studies; RA with &lt;25% crushed brick suitable for sub-base"/>
-        <s v="Aggregate per asphalt (kg/kg, 2016): 1.00 HI, 2.00 UMI, 3.24 LMI, 3.95 LI"/>
-        <s v="0.15 kg/kg concrete; 0.26 kg/kg timber; 0.25 kg/kg bricks"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Conditions" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Source" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Location" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Retrieval" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Pablo Busch" refreshedDate="46301.384375347225" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="103" xr:uid="{26772ACE-7642-4ECF-9F54-58FA3DD17438}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Pablo Busch" refreshedDate="46318.655374305556" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="103" xr:uid="{26772ACE-7642-4ECF-9F54-58FA3DD17438}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O104" sheet="Data"/>
   </cacheSource>
@@ -3160,9 +3057,74 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Pablo Busch" refreshedDate="46318.655374652779" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="29" xr:uid="{5C9B316A-7DF0-48F3-8AC8-536953F8B8F0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K30" sheet="Max_secondary_content"/>
+  </cacheSource>
+  <cacheFields count="11">
+    <cacheField name="Region / standard" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Your region" numFmtId="0">
+      <sharedItems count="9">
+        <s v="Oceania"/>
+        <s v="East Asia"/>
+        <s v="Europe &amp; Russia"/>
+        <s v="Global"/>
+        <s v="North America"/>
+        <s v="Latin America"/>
+        <s v="South Asia"/>
+        <s v="—"/>
+        <s v="All"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="End-use" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Recycled material" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Variable" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="Max building"/>
+        <s v="Max Roads"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Valid" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="2">
+        <n v="1"/>
+        <n v="0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Maximum share allowed / recommended" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Conditions" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Source" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Location" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Retrieval" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{15D971FD-66DB-4064-9D8E-FD2C3C0DC32C}" name="PT_Data" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="E7:L30" firstHeaderRow="1" firstDataRow="3" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{15D971FD-66DB-4064-9D8E-FD2C3C0DC32C}" name="PT_Data" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="E7:H15" firstHeaderRow="1" firstDataRow="3" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -3173,13 +3135,13 @@
         <item h="1" x="2"/>
         <item h="1" x="4"/>
         <item h="1" x="9"/>
-        <item h="1" x="1"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
+        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="11"/>
+        <item h="1" x="8"/>
         <item h="1" x="10"/>
-        <item x="7"/>
+        <item h="1" x="7"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -3344,99 +3306,37 @@
     <field x="4"/>
     <field x="6"/>
   </rowFields>
-  <rowItems count="21">
+  <rowItems count="6">
     <i>
       <x/>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="40"/>
-    </i>
-    <i r="1">
-      <x v="46"/>
+      <x v="27"/>
     </i>
     <i>
       <x v="2"/>
-      <x v="4"/>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="26"/>
     </i>
     <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="35"/>
+      <x v="31"/>
     </i>
     <i>
       <x v="5"/>
-      <x v="1"/>
+      <x v="41"/>
     </i>
     <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
+      <x v="44"/>
     </i>
   </rowItems>
   <colFields count="2">
     <field x="7"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="6">
+  <colItems count="2">
     <i>
-      <x/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="6"/>
+      <x v="2"/>
       <x/>
     </i>
     <i r="1" i="1">
@@ -3452,7 +3352,7 @@
     <dataField name="Count of Value" fld="10" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="14">
+    <format dxfId="6">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -3464,7 +3364,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="5">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -3490,7 +3390,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1E9560F-763A-4793-8526-C6A17A1829EB}" name="PT_Max_secondary_content" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1E9560F-763A-4793-8526-C6A17A1829EB}" name="PT_Max_secondary_content" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="E7:H21" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="11">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -3522,23 +3422,7 @@
         <item x="0"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="13">
-        <item x="9"/>
-        <item x="8"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="3"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -3610,7 +3494,7 @@
     <dataField name="Count of Maximum share allowed / recommended2" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="10">
+    <format dxfId="7">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -3644,40 +3528,40 @@
   <data>
     <tabular pivotCacheId="140362333">
       <items count="34">
-        <i x="25" s="1"/>
-        <i x="32" s="1"/>
-        <i x="23" s="1"/>
-        <i x="15" s="1"/>
-        <i x="30" s="1"/>
-        <i x="31" s="1"/>
-        <i x="9" s="1"/>
-        <i x="10" s="1"/>
-        <i x="0" s="1"/>
-        <i x="6" s="1"/>
-        <i x="26" s="1"/>
-        <i x="33" s="1"/>
-        <i x="28" s="1"/>
-        <i x="29" s="1"/>
+        <i x="18" s="1"/>
+        <i x="3" s="1"/>
+        <i x="1" s="1"/>
+        <i x="4" s="1"/>
+        <i x="5" s="1"/>
         <i x="17" s="1" nd="1"/>
         <i x="14" s="1" nd="1"/>
+        <i x="25" s="1" nd="1"/>
+        <i x="32" s="1" nd="1"/>
+        <i x="23" s="1" nd="1"/>
         <i x="27" s="1" nd="1"/>
         <i x="19" s="1" nd="1"/>
-        <i x="18" s="1" nd="1"/>
+        <i x="15" s="1" nd="1"/>
         <i x="13" s="1" nd="1"/>
-        <i x="3" s="1" nd="1"/>
+        <i x="30" s="1" nd="1"/>
+        <i x="31" s="1" nd="1"/>
+        <i x="9" s="1" nd="1"/>
         <i x="16" s="1" nd="1"/>
+        <i x="10" s="1" nd="1"/>
         <i x="7" s="1" nd="1"/>
         <i x="2" s="1" nd="1"/>
         <i x="22" s="1" nd="1"/>
-        <i x="1" s="1" nd="1"/>
+        <i x="0" s="1" nd="1"/>
+        <i x="6" s="1" nd="1"/>
         <i x="21" s="1" nd="1"/>
         <i x="11" s="1" nd="1"/>
         <i x="24" s="1" nd="1"/>
         <i x="12" s="1" nd="1"/>
         <i x="20" s="1" nd="1"/>
-        <i x="4" s="1" nd="1"/>
+        <i x="26" s="1" nd="1"/>
         <i x="8" s="1" nd="1"/>
-        <i x="5" s="1" nd="1"/>
+        <i x="33" s="1" nd="1"/>
+        <i x="28" s="1" nd="1"/>
+        <i x="29" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -3693,14 +3577,14 @@
     <tabular pivotCacheId="140362333">
       <items count="13">
         <i x="2"/>
-        <i x="3" s="1"/>
-        <i x="5" s="1"/>
-        <i x="11" s="1"/>
-        <i x="8" s="1"/>
-        <i x="1"/>
+        <i x="3"/>
+        <i x="5"/>
+        <i x="11"/>
+        <i x="8"/>
+        <i x="1" s="1"/>
         <i x="0"/>
         <i x="6"/>
-        <i x="7" s="1"/>
+        <i x="7"/>
         <i x="12" nd="1"/>
         <i x="4" nd="1"/>
         <i x="9" nd="1"/>
@@ -3984,20 +3868,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A99ADB4-F65F-4667-AE35-EB274FE87CCF}">
-  <dimension ref="E1:L30"/>
+  <dimension ref="E1:H15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="10.59765625" customWidth="1"/>
     <col min="4" max="4" width="22.46484375" customWidth="1"/>
     <col min="5" max="5" width="46.73046875" customWidth="1"/>
-    <col min="6" max="6" width="54.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="16.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="5:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="5:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="5:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="4" spans="5:8" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E4" s="27" t="s">
         <v>699</v>
       </c>
@@ -4005,15 +3890,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="5:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="5:8" x14ac:dyDescent="0.45">
       <c r="E5" s="27" t="s">
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="7" spans="5:12" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="5:8" x14ac:dyDescent="0.45">
       <c r="G7" s="27" t="s">
         <v>680</v>
       </c>
@@ -4021,18 +3906,12 @@
         <v>739</v>
       </c>
     </row>
-    <row r="8" spans="5:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="5:8" x14ac:dyDescent="0.45">
       <c r="G8" t="s">
-        <v>709</v>
-      </c>
-      <c r="I8" t="s">
-        <v>741</v>
-      </c>
-      <c r="K8" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="9" spans="5:12" x14ac:dyDescent="0.45">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="9" spans="5:8" x14ac:dyDescent="0.45">
       <c r="E9" s="27" t="s">
         <v>21</v>
       </c>
@@ -4045,358 +3924,84 @@
       <c r="H9" t="s">
         <v>740</v>
       </c>
-      <c r="I9" t="s">
-        <v>738</v>
-      </c>
-      <c r="J9" t="s">
-        <v>740</v>
-      </c>
-      <c r="K9" t="s">
-        <v>738</v>
-      </c>
-      <c r="L9" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="10" spans="5:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="5:8" x14ac:dyDescent="0.45">
       <c r="E10" t="s">
         <v>175</v>
       </c>
       <c r="F10" t="s">
-        <v>321</v>
+        <v>207</v>
       </c>
       <c r="G10" s="29">
-        <v>0.98</v>
+        <v>0.52</v>
       </c>
       <c r="H10" s="30">
         <v>1</v>
       </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-    </row>
-    <row r="11" spans="5:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="5:8" x14ac:dyDescent="0.45">
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
       <c r="F11" t="s">
-        <v>334</v>
+        <v>35</v>
       </c>
       <c r="G11" s="29">
-        <v>0.70500000000000007</v>
+        <v>0.61</v>
       </c>
       <c r="H11" s="30">
-        <v>3</v>
-      </c>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-    </row>
-    <row r="12" spans="5:12" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="5:8" x14ac:dyDescent="0.45">
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
       <c r="F12" t="s">
-        <v>255</v>
+        <v>87</v>
       </c>
       <c r="G12" s="29">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
       <c r="H12" s="30">
         <v>1</v>
       </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-    </row>
-    <row r="13" spans="5:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="5:8" x14ac:dyDescent="0.45">
       <c r="F13" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="G13" s="29">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="H13" s="30">
-        <v>1</v>
-      </c>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-    </row>
-    <row r="14" spans="5:12" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="5:8" x14ac:dyDescent="0.45">
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
       <c r="F14" t="s">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="G14" s="29">
-        <v>0.9</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H14" s="30">
         <v>1</v>
       </c>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-    </row>
-    <row r="15" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E15" t="s">
-        <v>33</v>
-      </c>
+    </row>
+    <row r="15" spans="5:8" x14ac:dyDescent="0.45">
       <c r="F15" t="s">
-        <v>311</v>
+        <v>62</v>
       </c>
       <c r="G15" s="29">
-        <v>0.8</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="H15" s="30">
         <v>1</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-    </row>
-    <row r="16" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F16" t="s">
-        <v>334</v>
-      </c>
-      <c r="G16" s="29">
-        <v>0.62891666666666679</v>
-      </c>
-      <c r="H16" s="30">
-        <v>12</v>
-      </c>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" s="29">
-        <v>0.95</v>
-      </c>
-      <c r="H17" s="30">
-        <v>1</v>
-      </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-    </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F18" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30">
-        <v>0.94699999999999995</v>
-      </c>
-      <c r="J18" s="30">
-        <v>1</v>
-      </c>
-      <c r="K18" s="30">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="L18" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F19" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="J19" s="30">
-        <v>1</v>
-      </c>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-    </row>
-    <row r="20" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F20" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L20" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E21" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" t="s">
-        <v>334</v>
-      </c>
-      <c r="G21" s="29">
-        <v>6.1400000000000003E-2</v>
-      </c>
-      <c r="H21" s="30">
-        <v>1</v>
-      </c>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-    </row>
-    <row r="22" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F22" t="s">
-        <v>306</v>
-      </c>
-      <c r="G22" s="29">
-        <v>0.3</v>
-      </c>
-      <c r="H22" s="30">
-        <v>1</v>
-      </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-    </row>
-    <row r="23" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>302</v>
-      </c>
-      <c r="G23" s="29">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H23" s="30">
-        <v>1</v>
-      </c>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-    </row>
-    <row r="24" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F24" t="s">
-        <v>334</v>
-      </c>
-      <c r="G24" s="29">
-        <v>0.39</v>
-      </c>
-      <c r="H24" s="30">
-        <v>2</v>
-      </c>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-    </row>
-    <row r="25" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F25" t="s">
-        <v>292</v>
-      </c>
-      <c r="G25" s="29">
-        <v>0.7</v>
-      </c>
-      <c r="H25" s="30">
-        <v>1</v>
-      </c>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-    </row>
-    <row r="26" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F26" t="s">
-        <v>334</v>
-      </c>
-      <c r="G26" s="29">
-        <v>0.622</v>
-      </c>
-      <c r="H26" s="30">
-        <v>1</v>
-      </c>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-    </row>
-    <row r="27" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F27" t="s">
-        <v>283</v>
-      </c>
-      <c r="G27" s="29">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H27" s="30">
-        <v>1</v>
-      </c>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-    </row>
-    <row r="28" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E28" t="s">
-        <v>481</v>
-      </c>
-      <c r="F28" t="s">
-        <v>334</v>
-      </c>
-      <c r="G28" s="29">
-        <v>0.32</v>
-      </c>
-      <c r="H28" s="30">
-        <v>1</v>
-      </c>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-    </row>
-    <row r="29" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E29" t="s">
-        <v>227</v>
-      </c>
-      <c r="F29" t="s">
-        <v>327</v>
-      </c>
-      <c r="G29" s="29">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="30">
-        <v>1</v>
-      </c>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-    </row>
-    <row r="30" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="F30" t="s">
-        <v>334</v>
-      </c>
-      <c r="G30" s="29">
-        <v>0.16</v>
-      </c>
-      <c r="H30" s="30">
-        <v>1</v>
-      </c>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
